--- a/mlef_pipeline/results/OS_24/IO_ONLY/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_24/IO_ONLY/training_summary.xlsx
@@ -552,34 +552,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6948495511245859</v>
+        <v>0.6983867041405715</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04255080269961442</v>
+        <v>0.04221285491131754</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5903065232237271</v>
+        <v>0.5990426428213531</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03374777209793722</v>
+        <v>0.03286437416564853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6125194331055462</v>
+        <v>0.6175048481148276</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06604858379157139</v>
+        <v>0.0670052193425924</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6488040652285361</v>
+        <v>0.6598904100977722</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08866385082058822</v>
+        <v>0.09677790704963812</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6925925925925926</v>
+        <v>0.6988425925925925</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09862173937003105</v>
+        <v>0.09675541891480288</v>
       </c>
       <c r="L2" t="n">
         <v>0.6990430622009569</v>
@@ -591,10 +591,10 @@
         <v>0.8611111111111112</v>
       </c>
       <c r="O2" t="n">
-        <v>0.53125</v>
+        <v>0.5345052083333334</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1341313927848509</v>
+        <v>0.1315406081750359</v>
       </c>
       <c r="Q2" t="n">
         <v>0.4320486815415822</v>
@@ -698,16 +698,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6902640264026403</v>
+        <v>0.6893399339933994</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0794952627529496</v>
+        <v>0.0797573831703744</v>
       </c>
       <c r="D4" t="n">
-        <v>0.646197091145139</v>
+        <v>0.6431680194137924</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06934499253847869</v>
+        <v>0.06997818849784557</v>
       </c>
       <c r="F4" t="n">
         <v>0.5647618737871445</v>
@@ -716,16 +716,16 @@
         <v>0.1268229253686974</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7729652179420453</v>
+        <v>0.768082976236699</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07138931089985803</v>
+        <v>0.07420296386623881</v>
       </c>
       <c r="J4" t="n">
-        <v>0.638961038961039</v>
+        <v>0.6441558441558441</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1810372694011812</v>
+        <v>0.1812325286675256</v>
       </c>
       <c r="L4" t="n">
         <v>0.4105363075462743</v>
@@ -737,10 +737,10 @@
         <v>0.2285714285714286</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6376470588235295</v>
+        <v>0.6447058823529411</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1860570217227608</v>
+        <v>0.1849870813869318</v>
       </c>
       <c r="Q4" t="n">
         <v>0.4447115384615384</v>
